--- a/esyluban/examples/dev/DataTables/test/path.xlsx
+++ b/esyluban/examples/dev/DataTables/test/path.xlsx
@@ -1009,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col width="44" customWidth="1" style="1" min="3" max="3"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbPath" &amp; value_type="test.Path" &amp; read_schema_from_file="false" &amp; input="test/path.xlsx" &amp; output="test_tbpath"</t>
+          <t>full_name="test.TbPath" &amp; input="test/path.xlsx"</t>
         </is>
       </c>
     </row>
@@ -1093,19 +1093,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
